--- a/docs/sprintB/PI-2023-24 Self-Assessment (1).xlsx
+++ b/docs/sprintB/PI-2023-24 Self-Assessment (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francisco\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/inesgomesoliveira/Desktop/lei-24-s2-g163/docs/sprintB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D74EDD-0322-4905-8814-35B1739A5BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CE6F1D-F78C-A040-9E46-191787DD1AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="23260" windowHeight="12580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Group and Self Assessment" sheetId="2" r:id="rId1"/>
@@ -1761,33 +1761,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:T36"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="5.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="19" width="7.8984375" customWidth="1"/>
+    <col min="4" max="19" width="7.83203125" customWidth="1"/>
     <col min="20" max="20" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
         <v>136</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1796,13 +1796,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:20" ht="15.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:20" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="E8" s="65" t="s">
@@ -1824,7 +1824,7 @@
       <c r="S8" s="66"/>
       <c r="T8" s="67"/>
     </row>
-    <row r="9" spans="1:20" ht="105.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="106" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="42">
@@ -1891,7 +1891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="62" t="s">
         <v>6</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="63"/>
       <c r="C11" s="8">
         <v>1220804</v>
@@ -1947,7 +1947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="63"/>
       <c r="C12" s="8">
         <v>1210527</v>
@@ -1974,7 +1974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="63"/>
       <c r="C13" s="8">
         <v>1231205</v>
@@ -2001,7 +2001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="63"/>
       <c r="C14" s="8">
         <v>1231502</v>
@@ -2028,7 +2028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="63"/>
       <c r="C15" s="8">
         <v>1230605</v>
@@ -2055,7 +2055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="63"/>
       <c r="C16" s="8" t="s">
         <v>7</v>
@@ -2080,7 +2080,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="63"/>
       <c r="C17" s="8" t="s">
         <v>8</v>
@@ -2105,7 +2105,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="63"/>
       <c r="C18" s="8" t="s">
         <v>9</v>
@@ -2130,7 +2130,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="63"/>
       <c r="C19" s="8" t="s">
         <v>10</v>
@@ -2155,7 +2155,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="63"/>
       <c r="C20" s="8" t="s">
         <v>11</v>
@@ -2180,7 +2180,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B21" s="63"/>
       <c r="C21" s="8" t="s">
         <v>12</v>
@@ -2205,7 +2205,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" s="63"/>
       <c r="C22" s="8" t="s">
         <v>13</v>
@@ -2230,7 +2230,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B23" s="63"/>
       <c r="C23" s="8" t="s">
         <v>14</v>
@@ -2255,7 +2255,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B24" s="64"/>
       <c r="C24" s="40" t="s">
         <v>15</v>
@@ -2280,7 +2280,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
       <c r="C25" s="45" t="s">
         <v>5</v>
@@ -2347,27 +2347,27 @@
       </c>
       <c r="S25" s="53"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>0</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>3</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>4</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2434,21 +2434,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultColWidth="20.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="20.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.5" customWidth="1"/>
     <col min="5" max="10" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="62" t="s">
         <v>27</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="63"/>
       <c r="B4" s="71"/>
       <c r="C4" s="71"/>
@@ -2504,7 +2504,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="52" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="63"/>
       <c r="B5" s="71"/>
       <c r="C5" s="71"/>
@@ -2528,7 +2528,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="14">
         <v>1</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="14">
         <v>2</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="14">
         <v>3</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="14">
         <v>4</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A10" s="14">
         <v>5</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="14">
         <v>6</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="14">
         <v>7</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="14">
         <v>8</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="14">
         <v>9</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A15" s="14">
         <v>10</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="14">
         <v>11</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A17" s="14">
         <v>12</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A18" s="14">
         <v>13</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="14">
         <v>14</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" s="14"/>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -2990,7 +2990,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" s="14"/>
       <c r="B21" s="29"/>
       <c r="C21" s="29"/>
@@ -3014,7 +3014,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A22" s="14"/>
       <c r="B22" s="29"/>
       <c r="C22" s="29"/>
@@ -3038,7 +3038,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A23" s="14"/>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -3062,7 +3062,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="14"/>
       <c r="B24" s="29"/>
       <c r="C24" s="29"/>
@@ -3086,7 +3086,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" ht="52" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="22"/>
       <c r="B25" s="54"/>
       <c r="C25" s="54"/>
@@ -3150,24 +3150,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Z10"/>
-  <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.8984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="17" width="5.59765625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="16.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="17" width="5.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="17.5" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="17" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="16.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="7.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="10.8984375" style="1"/>
+    <col min="26" max="26" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="21" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
         <v>46</v>
       </c>
@@ -3186,8 +3186,8 @@
       <c r="N1" s="13"/>
       <c r="O1" s="13"/>
     </row>
-    <row r="2" spans="1:26" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:26" ht="57" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:26" ht="57" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
         <v>47</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -3347,7 +3347,7 @@
       <c r="Y4" s="7"/>
       <c r="Z4" s="15"/>
     </row>
-    <row r="5" spans="1:26" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="119" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>56</v>
       </c>
@@ -3406,7 +3406,7 @@
       <c r="Y5" s="7"/>
       <c r="Z5" s="15"/>
     </row>
-    <row r="6" spans="1:26" ht="78" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="85" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
         <v>63</v>
       </c>
@@ -3465,7 +3465,7 @@
       <c r="Y6" s="7"/>
       <c r="Z6" s="15"/>
     </row>
-    <row r="7" spans="1:26" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
         <v>69</v>
       </c>
@@ -3524,7 +3524,7 @@
       <c r="Y7" s="7"/>
       <c r="Z7" s="15"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
         <v>45</v>
       </c>
@@ -3602,7 +3602,7 @@
       <c r="Y8" s="7"/>
       <c r="Z8" s="15"/>
     </row>
-    <row r="9" spans="1:26" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>75</v>
       </c>
@@ -3677,7 +3677,7 @@
       <c r="Y9" s="23"/>
       <c r="Z9" s="16"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
     </row>
   </sheetData>
@@ -3695,22 +3695,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:Z17"/>
-  <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.8984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="17" width="5.59765625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="16.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="17" width="5.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="20.59765625" style="1" customWidth="1"/>
+    <col min="22" max="24" width="20.6640625" style="1" customWidth="1"/>
     <col min="25" max="25" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="7.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="10.8984375" style="1"/>
+    <col min="26" max="26" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="21" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
         <v>76</v>
       </c>
@@ -3729,7 +3729,7 @@
       <c r="N1" s="13"/>
       <c r="O1" s="13"/>
     </row>
-    <row r="3" spans="1:26" ht="57" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="57" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
         <v>47</v>
       </c>
@@ -3830,7 +3830,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="144.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="144.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
         <v>77</v>
       </c>
@@ -3846,7 +3846,9 @@
       <c r="E4" s="25">
         <v>2</v>
       </c>
-      <c r="F4" s="25"/>
+      <c r="F4" s="25">
+        <v>3</v>
+      </c>
       <c r="G4" s="25">
         <v>2</v>
       </c>
@@ -3862,7 +3864,7 @@
       <c r="Q4" s="25"/>
       <c r="R4" s="55">
         <f t="shared" ref="R4:R7" si="0">AVERAGE(C4:Q4)</f>
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S4" s="59" t="s">
         <v>78</v>
@@ -3885,7 +3887,7 @@
       <c r="Y4" s="56"/>
       <c r="Z4" s="15"/>
     </row>
-    <row r="5" spans="1:26" ht="101.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="101.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>84</v>
       </c>
@@ -3899,7 +3901,9 @@
         <v>3</v>
       </c>
       <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
+      <c r="F5" s="25">
+        <v>4</v>
+      </c>
       <c r="G5" s="25"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
@@ -3936,7 +3940,7 @@
       <c r="Y5" s="56"/>
       <c r="Z5" s="15"/>
     </row>
-    <row r="6" spans="1:26" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
         <v>91</v>
       </c>
@@ -3950,7 +3954,9 @@
         <v>4</v>
       </c>
       <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
+      <c r="F6" s="25">
+        <v>5</v>
+      </c>
       <c r="G6" s="25"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
@@ -3964,7 +3970,7 @@
       <c r="Q6" s="25"/>
       <c r="R6" s="55">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="S6" s="59" t="s">
         <v>92</v>
@@ -3987,7 +3993,7 @@
       <c r="Y6" s="56"/>
       <c r="Z6" s="15"/>
     </row>
-    <row r="7" spans="1:26" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
         <v>98</v>
       </c>
@@ -4046,7 +4052,7 @@
       <c r="Y7" s="56"/>
       <c r="Z7" s="15"/>
     </row>
-    <row r="8" spans="1:26" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
         <v>104</v>
       </c>
@@ -4063,7 +4069,7 @@
         <v>5</v>
       </c>
       <c r="F8" s="25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="25">
         <v>5</v>
@@ -4082,7 +4088,7 @@
       <c r="Q8" s="25"/>
       <c r="R8" s="55">
         <f t="shared" ref="R8:R12" si="1">AVERAGE(C8:Q8)</f>
-        <v>4.5</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="S8" s="59" t="s">
         <v>92</v>
@@ -4105,7 +4111,7 @@
       <c r="Y8" s="56"/>
       <c r="Z8" s="15"/>
     </row>
-    <row r="9" spans="1:26" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" ht="68" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
         <v>110</v>
       </c>
@@ -4160,7 +4166,7 @@
       <c r="Y9" s="56"/>
       <c r="Z9" s="15"/>
     </row>
-    <row r="10" spans="1:26" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="102" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
         <v>115</v>
       </c>
@@ -4207,7 +4213,7 @@
       <c r="Y10" s="56"/>
       <c r="Z10" s="15"/>
     </row>
-    <row r="11" spans="1:26" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
         <v>121</v>
       </c>
@@ -4266,7 +4272,7 @@
       <c r="Y11" s="56"/>
       <c r="Z11" s="15"/>
     </row>
-    <row r="12" spans="1:26" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
         <v>127</v>
       </c>
@@ -4313,7 +4319,7 @@
       <c r="Y12" s="56"/>
       <c r="Z12" s="15"/>
     </row>
-    <row r="13" spans="1:26" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
         <v>128</v>
       </c>
@@ -4372,7 +4378,7 @@
       <c r="Y13" s="56"/>
       <c r="Z13" s="15"/>
     </row>
-    <row r="14" spans="1:26" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
         <v>135</v>
       </c>
@@ -4431,7 +4437,7 @@
       <c r="Y14" s="56"/>
       <c r="Z14" s="15"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
         <v>45</v>
       </c>
@@ -4453,7 +4459,7 @@
       </c>
       <c r="F15" s="7">
         <f t="shared" si="4"/>
-        <v>2.1</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="G15" s="7">
         <f t="shared" si="4"/>
@@ -4509,7 +4515,7 @@
       <c r="Y15" s="7"/>
       <c r="Z15" s="15"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="22" t="s">
         <v>75</v>
       </c>
@@ -4528,7 +4534,7 @@
       </c>
       <c r="F16" s="23">
         <f t="shared" si="5"/>
-        <v>8.4</v>
+        <v>12.600000000000001</v>
       </c>
       <c r="G16" s="23">
         <f t="shared" si="5"/>
@@ -4584,7 +4590,7 @@
       <c r="Y16" s="23"/>
       <c r="Z16" s="16"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
     </row>
   </sheetData>

--- a/docs/sprintB/PI-2023-24 Self-Assessment (1).xlsx
+++ b/docs/sprintB/PI-2023-24 Self-Assessment (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/inesgomesoliveira/Desktop/lei-24-s2-g163/docs/sprintB/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francisco\Desktop\lei-24-s2-1dp-g163\docs\sprintB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CE6F1D-F78C-A040-9E46-191787DD1AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6183F2F3-EE60-4361-94CE-B9585CDD6A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="23260" windowHeight="12580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Group and Self Assessment" sheetId="2" r:id="rId1"/>
@@ -1761,33 +1761,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:T36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.69921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="19" width="7.83203125" customWidth="1"/>
+    <col min="4" max="19" width="7.796875" customWidth="1"/>
     <col min="20" max="20" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>136</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1796,13 +1796,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:20" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:20" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="E8" s="65" t="s">
@@ -1824,7 +1824,7 @@
       <c r="S8" s="66"/>
       <c r="T8" s="67"/>
     </row>
-    <row r="9" spans="1:20" ht="106" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="106.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="42">
@@ -1891,7 +1891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="62" t="s">
         <v>6</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="63"/>
       <c r="C11" s="8">
         <v>1220804</v>
@@ -1947,7 +1947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="63"/>
       <c r="C12" s="8">
         <v>1210527</v>
@@ -1974,7 +1974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="63"/>
       <c r="C13" s="8">
         <v>1231205</v>
@@ -2001,7 +2001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="63"/>
       <c r="C14" s="8">
         <v>1231502</v>
@@ -2028,7 +2028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="63"/>
       <c r="C15" s="8">
         <v>1230605</v>
@@ -2055,7 +2055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="63"/>
       <c r="C16" s="8" t="s">
         <v>7</v>
@@ -2080,7 +2080,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="63"/>
       <c r="C17" s="8" t="s">
         <v>8</v>
@@ -2105,7 +2105,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="63"/>
       <c r="C18" s="8" t="s">
         <v>9</v>
@@ -2130,7 +2130,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="63"/>
       <c r="C19" s="8" t="s">
         <v>10</v>
@@ -2155,7 +2155,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="63"/>
       <c r="C20" s="8" t="s">
         <v>11</v>
@@ -2180,7 +2180,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="63"/>
       <c r="C21" s="8" t="s">
         <v>12</v>
@@ -2205,7 +2205,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="63"/>
       <c r="C22" s="8" t="s">
         <v>13</v>
@@ -2230,7 +2230,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="63"/>
       <c r="C23" s="8" t="s">
         <v>14</v>
@@ -2255,7 +2255,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="64"/>
       <c r="C24" s="40" t="s">
         <v>15</v>
@@ -2280,7 +2280,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="1"/>
       <c r="C25" s="45" t="s">
         <v>5</v>
@@ -2347,27 +2347,27 @@
       </c>
       <c r="S25" s="53"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>0</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>4</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2434,21 +2434,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:J25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="20.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="20.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.5" customWidth="1"/>
     <col min="5" max="10" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="30" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="62" t="s">
         <v>27</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="63"/>
       <c r="B4" s="71"/>
       <c r="C4" s="71"/>
@@ -2504,7 +2504,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="52" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="63"/>
       <c r="B5" s="71"/>
       <c r="C5" s="71"/>
@@ -2528,7 +2528,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>1</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
         <v>2</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>3</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
         <v>4</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>5</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
         <v>6</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>7</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A13" s="14">
         <v>8</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>9</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
         <v>10</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>11</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A17" s="14">
         <v>12</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>13</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A19" s="14">
         <v>14</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A20" s="14"/>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -2990,7 +2990,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A21" s="14"/>
       <c r="B21" s="29"/>
       <c r="C21" s="29"/>
@@ -3014,7 +3014,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A22" s="14"/>
       <c r="B22" s="29"/>
       <c r="C22" s="29"/>
@@ -3038,7 +3038,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A23" s="14"/>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -3062,7 +3062,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A24" s="14"/>
       <c r="B24" s="29"/>
       <c r="C24" s="29"/>
@@ -3086,7 +3086,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="52" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="22"/>
       <c r="B25" s="54"/>
       <c r="C25" s="54"/>
@@ -3150,24 +3150,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Z10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="17" width="5.6640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="17" width="5.69921875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="16.296875" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="17.5" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="17" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="16.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.296875" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="10.83203125" style="1"/>
+    <col min="26" max="26" width="8.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="7.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="10.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>46</v>
       </c>
@@ -3186,8 +3186,8 @@
       <c r="N1" s="13"/>
       <c r="O1" s="13"/>
     </row>
-    <row r="2" spans="1:26" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:26" ht="57" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:26" ht="57" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>47</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="68" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -3347,7 +3347,7 @@
       <c r="Y4" s="7"/>
       <c r="Z4" s="15"/>
     </row>
-    <row r="5" spans="1:26" ht="119" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>56</v>
       </c>
@@ -3406,7 +3406,7 @@
       <c r="Y5" s="7"/>
       <c r="Z5" s="15"/>
     </row>
-    <row r="6" spans="1:26" ht="85" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" ht="78" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>63</v>
       </c>
@@ -3465,7 +3465,7 @@
       <c r="Y6" s="7"/>
       <c r="Z6" s="15"/>
     </row>
-    <row r="7" spans="1:26" ht="102" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>69</v>
       </c>
@@ -3524,7 +3524,7 @@
       <c r="Y7" s="7"/>
       <c r="Z7" s="15"/>
     </row>
-    <row r="8" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>45</v>
       </c>
@@ -3602,7 +3602,7 @@
       <c r="Y8" s="7"/>
       <c r="Z8" s="15"/>
     </row>
-    <row r="9" spans="1:26" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
         <v>75</v>
       </c>
@@ -3677,7 +3677,7 @@
       <c r="Y9" s="23"/>
       <c r="Z9" s="16"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
     </row>
   </sheetData>
@@ -3695,22 +3695,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:Z17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="17" width="5.6640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="17" width="5.69921875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="16.296875" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="20.6640625" style="1" customWidth="1"/>
+    <col min="22" max="24" width="20.69921875" style="1" customWidth="1"/>
     <col min="25" max="25" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="10.83203125" style="1"/>
+    <col min="26" max="26" width="8.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="7.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="10.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>76</v>
       </c>
@@ -3729,7 +3729,7 @@
       <c r="N1" s="13"/>
       <c r="O1" s="13"/>
     </row>
-    <row r="3" spans="1:26" ht="57" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" ht="57" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>47</v>
       </c>
@@ -3830,7 +3830,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="144.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="144.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>77</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>0.1</v>
       </c>
       <c r="C4" s="25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="25">
         <v>3</v>
@@ -3852,7 +3852,9 @@
       <c r="G4" s="25">
         <v>2</v>
       </c>
-      <c r="H4" s="25"/>
+      <c r="H4" s="25">
+        <v>2</v>
+      </c>
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
       <c r="K4" s="25"/>
@@ -3864,7 +3866,7 @@
       <c r="Q4" s="25"/>
       <c r="R4" s="55">
         <f t="shared" ref="R4:R7" si="0">AVERAGE(C4:Q4)</f>
-        <v>2.8</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="S4" s="59" t="s">
         <v>78</v>
@@ -3887,7 +3889,7 @@
       <c r="Y4" s="56"/>
       <c r="Z4" s="15"/>
     </row>
-    <row r="5" spans="1:26" ht="101.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="101.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>84</v>
       </c>
@@ -3900,12 +3902,18 @@
       <c r="D5" s="25">
         <v>3</v>
       </c>
-      <c r="E5" s="25"/>
+      <c r="E5" s="25">
+        <v>2</v>
+      </c>
       <c r="F5" s="25">
-        <v>4</v>
-      </c>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
+        <v>2</v>
+      </c>
+      <c r="G5" s="25">
+        <v>2</v>
+      </c>
+      <c r="H5" s="25">
+        <v>2</v>
+      </c>
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25"/>
@@ -3917,7 +3925,7 @@
       <c r="Q5" s="25"/>
       <c r="R5" s="55">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="S5" s="59" t="s">
         <v>85</v>
@@ -3940,7 +3948,7 @@
       <c r="Y5" s="56"/>
       <c r="Z5" s="15"/>
     </row>
-    <row r="6" spans="1:26" ht="51" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>91</v>
       </c>
@@ -3993,7 +4001,7 @@
       <c r="Y6" s="56"/>
       <c r="Z6" s="15"/>
     </row>
-    <row r="7" spans="1:26" ht="51" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>98</v>
       </c>
@@ -4052,7 +4060,7 @@
       <c r="Y7" s="56"/>
       <c r="Z7" s="15"/>
     </row>
-    <row r="8" spans="1:26" ht="68" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>104</v>
       </c>
@@ -4111,7 +4119,7 @@
       <c r="Y8" s="56"/>
       <c r="Z8" s="15"/>
     </row>
-    <row r="9" spans="1:26" ht="68" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>110</v>
       </c>
@@ -4166,7 +4174,7 @@
       <c r="Y9" s="56"/>
       <c r="Z9" s="15"/>
     </row>
-    <row r="10" spans="1:26" ht="102" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>115</v>
       </c>
@@ -4213,7 +4221,7 @@
       <c r="Y10" s="56"/>
       <c r="Z10" s="15"/>
     </row>
-    <row r="11" spans="1:26" ht="34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>121</v>
       </c>
@@ -4272,7 +4280,7 @@
       <c r="Y11" s="56"/>
       <c r="Z11" s="15"/>
     </row>
-    <row r="12" spans="1:26" ht="34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>127</v>
       </c>
@@ -4319,7 +4327,7 @@
       <c r="Y12" s="56"/>
       <c r="Z12" s="15"/>
     </row>
-    <row r="13" spans="1:26" ht="51" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>128</v>
       </c>
@@ -4378,7 +4386,7 @@
       <c r="Y13" s="56"/>
       <c r="Z13" s="15"/>
     </row>
-    <row r="14" spans="1:26" ht="34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>135</v>
       </c>
@@ -4437,7 +4445,7 @@
       <c r="Y14" s="56"/>
       <c r="Z14" s="15"/>
     </row>
-    <row r="15" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>45</v>
       </c>
@@ -4447,7 +4455,7 @@
       </c>
       <c r="C15" s="7">
         <f>SUMPRODUCT(C4:C14,$B$4:$B$14)</f>
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" ref="D15:Q15" si="4">SUMPRODUCT(D4:D14,$B$4:$B$14)</f>
@@ -4455,19 +4463,19 @@
       </c>
       <c r="E15" s="7">
         <f t="shared" si="4"/>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="F15" s="7">
         <f t="shared" si="4"/>
-        <v>3.1500000000000004</v>
+        <v>2.95</v>
       </c>
       <c r="G15" s="7">
         <f t="shared" si="4"/>
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="H15" s="7">
         <f t="shared" si="4"/>
-        <v>2.2000000000000002</v>
+        <v>2.6</v>
       </c>
       <c r="I15" s="7">
         <f t="shared" si="4"/>
@@ -4515,14 +4523,14 @@
       <c r="Y15" s="7"/>
       <c r="Z15" s="15"/>
     </row>
-    <row r="16" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>75</v>
       </c>
       <c r="B16" s="23"/>
       <c r="C16" s="23">
         <f>C15/5*20</f>
-        <v>15.600000000000001</v>
+        <v>16</v>
       </c>
       <c r="D16" s="23">
         <f t="shared" ref="D16:Q16" si="5">D15/5*20</f>
@@ -4530,19 +4538,19 @@
       </c>
       <c r="E16" s="23">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="F16" s="23">
         <f t="shared" si="5"/>
-        <v>12.600000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="G16" s="23">
         <f t="shared" si="5"/>
-        <v>10.600000000000001</v>
+        <v>11.400000000000002</v>
       </c>
       <c r="H16" s="23">
         <f t="shared" si="5"/>
-        <v>8.8000000000000007</v>
+        <v>10.4</v>
       </c>
       <c r="I16" s="23">
         <f t="shared" si="5"/>
@@ -4590,7 +4598,7 @@
       <c r="Y16" s="23"/>
       <c r="Z16" s="16"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
     </row>
   </sheetData>
@@ -4789,18 +4797,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4822,14 +4830,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8D82CB-2E6F-4A14-B6B4-DFDD1BBD70FC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -4843,4 +4843,12 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>